--- a/wxdgaming.game.basic/src/main/cfg/任务成就.xlsx
+++ b/wxdgaming.game.basic/src/main/cfg/任务成就.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="q_task" sheetId="4" r:id="rId1"/>
@@ -338,7 +338,7 @@
     <t>[{"k1":"KillMonster","update":"Add","target":10}]</t>
   </si>
   <si>
-    <t>1|10,3|10,5|10</t>
+    <t>1|10#3|10#5|10</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":20}]</t>
@@ -347,7 +347,7 @@
     <t>1|1</t>
   </si>
   <si>
-    <t>1|10,3|10,5|11</t>
+    <t>1|10#3|10#5|11</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":30}]</t>
@@ -356,7 +356,7 @@
     <t>1|2</t>
   </si>
   <si>
-    <t>1|10,3|10,5|12</t>
+    <t>1|10#3|10#5|12</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":40}]</t>
@@ -365,7 +365,7 @@
     <t>1|3</t>
   </si>
   <si>
-    <t>1|10,3|10,5|13</t>
+    <t>1|10#3|10#5|13</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":50}]</t>
@@ -374,7 +374,7 @@
     <t>1|4</t>
   </si>
   <si>
-    <t>1|10,3|10,5|14</t>
+    <t>1|10#3|10#5|14</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":60}]</t>
@@ -383,7 +383,7 @@
     <t>1|5</t>
   </si>
   <si>
-    <t>1|10,3|10,5|15</t>
+    <t>1|10#3|10#5|15</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":70}]</t>
@@ -392,7 +392,7 @@
     <t>1|6</t>
   </si>
   <si>
-    <t>1|10,3|10,5|16</t>
+    <t>1|10#3|10#5|16</t>
   </si>
   <si>
     <t>等级提升</t>
@@ -407,7 +407,7 @@
     <t>1|7</t>
   </si>
   <si>
-    <t>1|10,3|10,5|17</t>
+    <t>1|10#3|10#5|17</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":100}]</t>
@@ -416,7 +416,7 @@
     <t>1|8</t>
   </si>
   <si>
-    <t>1|10,3|10,5|18</t>
+    <t>1|10#3|10#5|18</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":150}]</t>
@@ -425,7 +425,7 @@
     <t>1|9</t>
   </si>
   <si>
-    <t>1|10,3|10,5|19</t>
+    <t>1|10#3|10#5|19</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":200}]</t>
@@ -434,7 +434,7 @@
     <t>1|10</t>
   </si>
   <si>
-    <t>1|10,3|10,5|20</t>
+    <t>1|10#3|10#5|20</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":250}]</t>
@@ -443,7 +443,7 @@
     <t>1|11</t>
   </si>
   <si>
-    <t>1|10,3|10,5|21</t>
+    <t>1|10#3|10#5|21</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":300}]</t>
@@ -452,7 +452,7 @@
     <t>1|12</t>
   </si>
   <si>
-    <t>1|10,3|10,5|22</t>
+    <t>1|10#3|10#5|22</t>
   </si>
   <si>
     <t>[{"k1":"Lv","update":"Replace","target":10}]</t>
@@ -461,7 +461,7 @@
     <t>1|13</t>
   </si>
   <si>
-    <t>1|10,3|10,5|23</t>
+    <t>1|10#3|10#5|23</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":500}]</t>
@@ -470,7 +470,7 @@
     <t>1|14</t>
   </si>
   <si>
-    <t>1|10,3|10,5|24</t>
+    <t>1|10#3|10#5|24</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":800}]</t>
@@ -479,7 +479,7 @@
     <t>1|15</t>
   </si>
   <si>
-    <t>1|10,3|10,5|25</t>
+    <t>1|10#3|10#5|25</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":1100}]</t>
@@ -488,7 +488,7 @@
     <t>1|16</t>
   </si>
   <si>
-    <t>1|10,3|10,5|26</t>
+    <t>1|10#3|10#5|26</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":1400}]</t>
@@ -497,7 +497,7 @@
     <t>1|17</t>
   </si>
   <si>
-    <t>1|10,3|10,5|27</t>
+    <t>1|10#3|10#5|27</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":1700}]</t>
@@ -506,7 +506,7 @@
     <t>1|18</t>
   </si>
   <si>
-    <t>1|10,3|10,5|28</t>
+    <t>1|10#3|10#5|28</t>
   </si>
   <si>
     <t>成就集合</t>

--- a/wxdgaming.game.basic/src/main/cfg/任务成就.xlsx
+++ b/wxdgaming.game.basic/src/main/cfg/任务成就.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="q_task" sheetId="4" r:id="rId1"/>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="140">
   <si>
     <t>任务集合</t>
   </si>
@@ -332,262 +332,319 @@
     <t>击杀 {} 只怪物</t>
   </si>
   <si>
-    <t>Level|gte|1;Level|lte|999</t>
+    <t>Level#gte#1&amp;Level#lte#999</t>
   </si>
   <si>
     <t>[{"k1":"KillMonster","update":"Add","target":10}]</t>
   </si>
   <si>
+    <t>1#10#3#10#5#10</t>
+  </si>
+  <si>
+    <t>[{"k1":"KillMonster","update":"Add","target":20}]</t>
+  </si>
+  <si>
+    <t>1#1</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#11</t>
+  </si>
+  <si>
+    <t>[{"k1":"KillMonster","update":"Add","target":30}]</t>
+  </si>
+  <si>
+    <t>1#2</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#12</t>
+  </si>
+  <si>
+    <t>[{"k1":"KillMonster","update":"Add","target":40}]</t>
+  </si>
+  <si>
+    <t>1#3</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#13</t>
+  </si>
+  <si>
+    <t>[{"k1":"KillMonster","update":"Add","target":50}]</t>
+  </si>
+  <si>
+    <t>1#4</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#14</t>
+  </si>
+  <si>
+    <t>[{"k1":"KillMonster","update":"Add","target":60}]</t>
+  </si>
+  <si>
+    <t>1#5</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#15</t>
+  </si>
+  <si>
+    <t>[{"k1":"KillMonster","update":"Add","target":70}]</t>
+  </si>
+  <si>
+    <t>1#6</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#16</t>
+  </si>
+  <si>
+    <t>等级提升</t>
+  </si>
+  <si>
+    <t>等级提升至 {} 级</t>
+  </si>
+  <si>
+    <t>[{"k1":"Lv","update":"Replace","target":5}]</t>
+  </si>
+  <si>
+    <t>1#7</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#17</t>
+  </si>
+  <si>
+    <t>[{"k1":"KillMonster","update":"Add","target":100}]</t>
+  </si>
+  <si>
+    <t>1#8</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#18</t>
+  </si>
+  <si>
+    <t>[{"k1":"KillMonster","update":"Add","target":150}]</t>
+  </si>
+  <si>
+    <t>1#9</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#19</t>
+  </si>
+  <si>
+    <t>[{"k1":"KillMonster","update":"Add","target":200}]</t>
+  </si>
+  <si>
+    <t>1#10</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#20</t>
+  </si>
+  <si>
+    <t>[{"k1":"KillMonster","update":"Add","target":250}]</t>
+  </si>
+  <si>
+    <t>1#11</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#21</t>
+  </si>
+  <si>
+    <t>[{"k1":"KillMonster","update":"Add","target":300}]</t>
+  </si>
+  <si>
+    <t>1#12</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#22</t>
+  </si>
+  <si>
+    <t>[{"k1":"Lv","update":"Replace","target":10}]</t>
+  </si>
+  <si>
+    <t>1#13</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#23</t>
+  </si>
+  <si>
+    <t>[{"k1":"KillMonster","update":"Add","target":500}]</t>
+  </si>
+  <si>
+    <t>1#14</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#24</t>
+  </si>
+  <si>
+    <t>[{"k1":"KillMonster","update":"Add","target":800}]</t>
+  </si>
+  <si>
+    <t>1#15</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#25</t>
+  </si>
+  <si>
+    <t>[{"k1":"KillMonster","update":"Add","target":1100}]</t>
+  </si>
+  <si>
+    <t>1#16</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#26</t>
+  </si>
+  <si>
+    <t>[{"k1":"KillMonster","update":"Add","target":1400}]</t>
+  </si>
+  <si>
+    <t>1#17</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#27</t>
+  </si>
+  <si>
+    <t>[{"k1":"KillMonster","update":"Add","target":1700}]</t>
+  </si>
+  <si>
+    <t>1#18</t>
+  </si>
+  <si>
+    <t>1#10#3#10#5#28</t>
+  </si>
+  <si>
+    <t>成就集合</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>wxdgaming.boot2.core.lang.condition.Condition</t>
+  </si>
+  <si>
+    <t>成就类型</t>
+  </si>
+  <si>
+    <t>成就名称</t>
+  </si>
+  <si>
+    <t>成就说明</t>
+  </si>
+  <si>
+    <t>升级</t>
+  </si>
+  <si>
+    <t>{"k1":"Lv","update":"Max","target":1}</t>
+  </si>
+  <si>
     <t>1|10#3|10#5|10</t>
   </si>
   <si>
-    <t>[{"k1":"KillMonster","update":"Add","target":20}]</t>
-  </si>
-  <si>
-    <t>1|1</t>
+    <t>{"k1":"Lv","update":"Max","target":2}</t>
   </si>
   <si>
     <t>1|10#3|10#5|11</t>
   </si>
   <si>
-    <t>[{"k1":"KillMonster","update":"Add","target":30}]</t>
-  </si>
-  <si>
-    <t>1|2</t>
+    <t>{"k1":"Lv","update":"Max","target":3}</t>
   </si>
   <si>
     <t>1|10#3|10#5|12</t>
   </si>
   <si>
-    <t>[{"k1":"KillMonster","update":"Add","target":40}]</t>
-  </si>
-  <si>
-    <t>1|3</t>
+    <t>{"k1":"Lv","update":"Max","target":4}</t>
   </si>
   <si>
     <t>1|10#3|10#5|13</t>
   </si>
   <si>
-    <t>[{"k1":"KillMonster","update":"Add","target":50}]</t>
-  </si>
-  <si>
-    <t>1|4</t>
+    <t>{"k1":"Lv","update":"Max","target":5}</t>
   </si>
   <si>
     <t>1|10#3|10#5|14</t>
   </si>
   <si>
-    <t>[{"k1":"KillMonster","update":"Add","target":60}]</t>
-  </si>
-  <si>
-    <t>1|5</t>
+    <t>{"k1":"Lv","update":"Max","target":6}</t>
   </si>
   <si>
     <t>1|10#3|10#5|15</t>
   </si>
   <si>
-    <t>[{"k1":"KillMonster","update":"Add","target":70}]</t>
-  </si>
-  <si>
-    <t>1|6</t>
+    <t>{"k1":"Lv","update":"Max","target":7}</t>
   </si>
   <si>
     <t>1|10#3|10#5|16</t>
   </si>
   <si>
-    <t>等级提升</t>
-  </si>
-  <si>
-    <t>等级提升至 {} 级</t>
-  </si>
-  <si>
-    <t>[{"k1":"Lv","update":"Replace","target":5}]</t>
-  </si>
-  <si>
-    <t>1|7</t>
+    <t>{"k1":"Lv","update":"Max","target":8}</t>
   </si>
   <si>
     <t>1|10#3|10#5|17</t>
   </si>
   <si>
-    <t>[{"k1":"KillMonster","update":"Add","target":100}]</t>
-  </si>
-  <si>
-    <t>1|8</t>
+    <t>{"k1":"Lv","update":"Max","target":9}</t>
   </si>
   <si>
     <t>1|10#3|10#5|18</t>
   </si>
   <si>
-    <t>[{"k1":"KillMonster","update":"Add","target":150}]</t>
-  </si>
-  <si>
-    <t>1|9</t>
+    <t>{"k1":"KillMonster","update":"Add","target":200}</t>
   </si>
   <si>
     <t>1|10#3|10#5|19</t>
   </si>
   <si>
-    <t>[{"k1":"KillMonster","update":"Add","target":200}]</t>
-  </si>
-  <si>
-    <t>1|10</t>
+    <t>{"k1":"KillMonster","update":"Add","target":500}</t>
   </si>
   <si>
     <t>1|10#3|10#5|20</t>
   </si>
   <si>
-    <t>[{"k1":"KillMonster","update":"Add","target":250}]</t>
-  </si>
-  <si>
-    <t>1|11</t>
+    <t>{"k1":"KillMonster","update":"Add","target":800}</t>
   </si>
   <si>
     <t>1|10#3|10#5|21</t>
   </si>
   <si>
-    <t>[{"k1":"KillMonster","update":"Add","target":300}]</t>
-  </si>
-  <si>
-    <t>1|12</t>
+    <t>{"k1":"KillMonster","update":"Add","target":1100}</t>
   </si>
   <si>
     <t>1|10#3|10#5|22</t>
   </si>
   <si>
-    <t>[{"k1":"Lv","update":"Replace","target":10}]</t>
-  </si>
-  <si>
-    <t>1|13</t>
+    <t>{"k1":"KillMonster","update":"Add","target":1400}</t>
   </si>
   <si>
     <t>1|10#3|10#5|23</t>
   </si>
   <si>
-    <t>[{"k1":"KillMonster","update":"Add","target":500}]</t>
-  </si>
-  <si>
-    <t>1|14</t>
+    <t>{"k1":"KillMonster","update":"Add","target":1700}</t>
   </si>
   <si>
     <t>1|10#3|10#5|24</t>
   </si>
   <si>
-    <t>[{"k1":"KillMonster","update":"Add","target":800}]</t>
-  </si>
-  <si>
-    <t>1|15</t>
+    <t>{"k1":"KillMonster","update":"Add","target":2000}</t>
   </si>
   <si>
     <t>1|10#3|10#5|25</t>
   </si>
   <si>
-    <t>[{"k1":"KillMonster","update":"Add","target":1100}]</t>
-  </si>
-  <si>
-    <t>1|16</t>
+    <t>{"k1":"KillMonster","update":"Add","target":2300}</t>
   </si>
   <si>
     <t>1|10#3|10#5|26</t>
   </si>
   <si>
-    <t>[{"k1":"KillMonster","update":"Add","target":1400}]</t>
-  </si>
-  <si>
-    <t>1|17</t>
+    <t>{"k1":"KillMonster","update":"Add","target":2600}</t>
   </si>
   <si>
     <t>1|10#3|10#5|27</t>
   </si>
   <si>
-    <t>[{"k1":"KillMonster","update":"Add","target":1700}]</t>
-  </si>
-  <si>
-    <t>1|18</t>
+    <t>{"k1":"KillMonster","update":"Add","target":2900}</t>
   </si>
   <si>
     <t>1|10#3|10#5|28</t>
-  </si>
-  <si>
-    <t>成就集合</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>condition</t>
-  </si>
-  <si>
-    <t>wxdgaming.boot2.core.lang.condition.Condition</t>
-  </si>
-  <si>
-    <t>成就类型</t>
-  </si>
-  <si>
-    <t>成就名称</t>
-  </si>
-  <si>
-    <t>成就说明</t>
-  </si>
-  <si>
-    <t>升级</t>
-  </si>
-  <si>
-    <t>{"k1":"Lv","update":"Max","target":1}</t>
-  </si>
-  <si>
-    <t>{"k1":"Lv","update":"Max","target":2}</t>
-  </si>
-  <si>
-    <t>{"k1":"Lv","update":"Max","target":3}</t>
-  </si>
-  <si>
-    <t>{"k1":"Lv","update":"Max","target":4}</t>
-  </si>
-  <si>
-    <t>{"k1":"Lv","update":"Max","target":5}</t>
-  </si>
-  <si>
-    <t>{"k1":"Lv","update":"Max","target":6}</t>
-  </si>
-  <si>
-    <t>{"k1":"Lv","update":"Max","target":7}</t>
-  </si>
-  <si>
-    <t>{"k1":"Lv","update":"Max","target":8}</t>
-  </si>
-  <si>
-    <t>{"k1":"Lv","update":"Max","target":9}</t>
-  </si>
-  <si>
-    <t>{"k1":"KillMonster","update":"Add","target":200}</t>
-  </si>
-  <si>
-    <t>{"k1":"KillMonster","update":"Add","target":500}</t>
-  </si>
-  <si>
-    <t>{"k1":"KillMonster","update":"Add","target":800}</t>
-  </si>
-  <si>
-    <t>{"k1":"KillMonster","update":"Add","target":1100}</t>
-  </si>
-  <si>
-    <t>{"k1":"KillMonster","update":"Add","target":1400}</t>
-  </si>
-  <si>
-    <t>{"k1":"KillMonster","update":"Add","target":1700}</t>
-  </si>
-  <si>
-    <t>{"k1":"KillMonster","update":"Add","target":2000}</t>
-  </si>
-  <si>
-    <t>{"k1":"KillMonster","update":"Add","target":2300}</t>
-  </si>
-  <si>
-    <t>{"k1":"KillMonster","update":"Add","target":2600}</t>
-  </si>
-  <si>
-    <t>{"k1":"KillMonster","update":"Add","target":2900}</t>
   </si>
 </sst>
 </file>
@@ -2756,7 +2813,7 @@
         <v>102</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2779,10 +2836,10 @@
         <v>100</v>
       </c>
       <c r="G7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2805,10 +2862,10 @@
         <v>100</v>
       </c>
       <c r="G8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2831,10 +2888,10 @@
         <v>100</v>
       </c>
       <c r="G9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2857,10 +2914,10 @@
         <v>100</v>
       </c>
       <c r="G10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2883,10 +2940,10 @@
         <v>100</v>
       </c>
       <c r="G11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2909,10 +2966,10 @@
         <v>100</v>
       </c>
       <c r="G12" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2935,10 +2992,10 @@
         <v>100</v>
       </c>
       <c r="G13" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2961,10 +3018,10 @@
         <v>100</v>
       </c>
       <c r="G14" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2987,10 +3044,10 @@
         <v>100</v>
       </c>
       <c r="G15" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -3013,10 +3070,10 @@
         <v>100</v>
       </c>
       <c r="G16" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3039,10 +3096,10 @@
         <v>100</v>
       </c>
       <c r="G17" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -3065,10 +3122,10 @@
         <v>100</v>
       </c>
       <c r="G18" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -3091,10 +3148,10 @@
         <v>100</v>
       </c>
       <c r="G19" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -3117,10 +3174,10 @@
         <v>100</v>
       </c>
       <c r="G20" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -3143,10 +3200,10 @@
         <v>100</v>
       </c>
       <c r="G21" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>84</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -3169,10 +3226,10 @@
         <v>100</v>
       </c>
       <c r="G22" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3195,10 +3252,10 @@
         <v>100</v>
       </c>
       <c r="G23" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -3221,10 +3278,10 @@
         <v>100</v>
       </c>
       <c r="G24" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>93</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
